--- a/lead_research/leads.xlsx
+++ b/lead_research/leads.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -438,9 +438,11 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="90" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="90" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,15 +523,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>opening_line</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>opening_source_url</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>email_body</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>research_note</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -607,23 +619,28 @@
           <t>White-label web design for Idaho Websites</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Hi Jennie,
-I read your Boise business guide to getting found in ChatGPT and Gemini. It's a smart angle, and it tells me you're thinking about what a site has to do now, not just how it looks.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jennie,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Blog post on SEO and AI search for Boise businesses https://idahowebsites.com/the-boise-business-guide-to-seo-ai-search-how-to-get-your-site-found-by-chatgpt-gemini/</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -705,23 +722,28 @@
           <t>White-label web design for Espy Solutions</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Hi Matt,
-I went through your Colorado Adventure Guides case study. Pairing the redesign with the SEO work so the traffic actually grew is the kind of result clients remember.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Hey Matt,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Case study, Colorado Adventure Guides https://espysolutions.com/web-design-case-studies/colorado-adventure-guides/</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -799,23 +821,28 @@
           <t>Extra design capacity for Tag Team Design</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Hi Kyle,
-Your post on content writing in web design made a point I agree with, the site has to tell the brand's story before anyone cares about the layout.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kyle,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>Blog post on content writing in web design https://www.tagteamdesign.com/content-writing-in-web-design-building-a-website-that-tells-your-brands-story/</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -893,23 +920,28 @@
           <t>White-label web design for Cornerstone Web Studio</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Hi Mark,
-Your Google Ads case study with the 10x ROI caught my eye. When the ads are that good, the site they land on has to hold up its end.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mark,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>Case study, 10x ROI with Google Ads https://cornerstone.studio/10x-roi-google-ads/</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -987,23 +1019,28 @@
           <t>White-label web design for Perspektiiv Design Co.</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Hi Alison,
-I like that you run the studio from both Portland and Denver and build brands around founders. That founder-first approach usually shows in the websites too.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alison,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>About page, studio for founders with hubs in Portland and Denver https://perspektiiv.com/aboutperspektiiv</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1081,23 +1118,28 @@
           <t>Design help for JYZ Design client sites</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Hi Judy,
-I saw you do packaging design as well as websites. Carrying a brand from the box to the site is something most agencies only talk about.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Hey Judy,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>Packaging design and branding page https://jyzdesign.com/packaging-design/</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1175,23 +1217,28 @@
           <t>Design help for Muletown Digital client sites</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Hi Adam,
-I read that you toured as a session drummer out of Nashville before starting Muletown. Keeping tempo for a band sounds like decent training for keeping client projects on time.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adam,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Adam's team bio, former touring and session drummer https://muletowndigital.com/about/team/adam-silverman/</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1269,23 +1316,28 @@
           <t>Extra design capacity for Azuro Digital</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Hi Daniel,
-Your roundup of the best therapist website designs was a good read. You clearly study what works in a niche before you design for it.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Hey Daniel,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>Blog, 10 Best Therapist Website Designs of 2026 https://azurodigital.com/therapist-website-examples/</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1363,23 +1415,28 @@
           <t>Extra design capacity for Marvel Marketing</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Hi Ryan,
-I read that you started Marvel after building and selling a construction company at 21 by leaning on digital marketing. That's a better origin story than most agencies have.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ryan,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Founder page, built and sold a construction company at 21 https://marvelmarketing.ca/ryan-mcrae/</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1457,23 +1514,28 @@
           <t>Extra design capacity for Redfox Visual</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Hi Josh,
-I noticed you pair web design with video production, which not many Boise shops do under one roof.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josh,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>Video marketing plus website design categories on their blog https://www.redfoxvisual.com/category/video-marketing/</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1551,23 +1613,28 @@
           <t>White-label web design for Life Web &amp; Design</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Hi Alex,
-I like how upfront your homepage is about keeping the team small so pricing stays fair. That's exactly the setup where an outside design partner adds capacity without adding overhead.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Hey Alex,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>Homepage, small team with low overhead and competitive pricing https://www.lifewebanddesign.com/</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1649,23 +1716,28 @@
           <t>Design help for Bethany Works client sites</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Hi Bethany,
-Your Brandcend offer caught my eye. Building brands around how buyers actually behave is a much stronger pitch than just making things look nice.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Hey Bethany,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Brandcend, bespoke brand evolution offer https://bethanyworks.com/brandcend/</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1743,23 +1815,28 @@
           <t>Extra design capacity for Bullfinch</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Hi Kyle,
-I noticed you run Bullfinch as a fully remote team spread around Colorado, with pages for towns like Ridgway and Grand Junction. Covering small markets like that takes real focus.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kyle,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Colorado web design blog and town pages https://bullfinch.io/blog/colorado-web-design/</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1837,23 +1914,28 @@
           <t>White-label web design for Just By Design</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Hi Justine,
-I read your piece on the dental website that converts new patients. It's rare to see an agency write that specifically about one kind of client.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Hey Justine,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Article, the dental website that converts new patients https://justbydesign.com/seo-ai-marketing-resources/digital-strategy-marketing/dental-website-that-converts/</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -1931,23 +2013,28 @@
           <t>White-label web design for Thrive Web Designs</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Hi Josh,
-Fifteen years of custom sites for Idaho businesses is a long run. I imagine the busy seasons get pretty full.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josh,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>About page, founded 2010, custom web design in Boise https://www.thrivewebdesigns.com/about/</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2025,23 +2112,28 @@
           <t>Design help for Lake Design Co. client sites</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Hi Christine,
-Your Page-in-a-Day offer is a clever way to package design work. Clients love knowing exactly what they get and when.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Hey Christine,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Page-in-a-Day website offer https://www.lakedesignmn.com/page-in-a-day-website</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2119,23 +2211,28 @@
           <t>Extra design capacity for The Mighty Mo!</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Hi Toby,
-Eighteen years of WordPress work plus an unlimited support plan tells me your clients stick around. That usually means a steady stream of redesigns too.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Hey Toby,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Unlimited WordPress support offer https://themightymo.com/unlimited-wordpress-support/</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2217,23 +2314,28 @@
           <t>Design help for Idea Marketing client sites</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Hi Lucia,
-Your VIP Design Day is a smart offer. Turning a site around in a day means the design side has to be locked in fast.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Hey Lucia,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>VIP Design Day offer https://ideamarketing.ca/vip-design-day/</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2311,23 +2413,28 @@
           <t>Extra design capacity for Webconsuls</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Hi Dennis,
-I enjoyed your post on the story behind the Webconsuls name. Twenty-five years in, that origin story still holds up.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dennis,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Blog, the story behind the Webconsuls name https://www.webconsuls.com/blog/2019/05/webconsuls-business-name/</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2409,23 +2516,28 @@
           <t>Extra design capacity for Generate Design</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Hi Paul,
-I read how you and Tiffany met studying graphic design at Iowa State and started Generate in 1998. That's a long run for a studio.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Hey Paul,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>How it all started page https://generatedesign.com/design-agency-raleigh/</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2503,23 +2615,28 @@
           <t>White-label web design for Chariot Creative</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Hi Jason,
-Congrats on the 2026 Webby. That's a big one for an independent shop in Raleigh.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jason,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Homepage, 2026 Webby Award winner https://chariotcreative.com/</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2601,23 +2718,28 @@
           <t>Extra design capacity for TMS Digital</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>Hi Jeff,
-I liked your About page, running the agency with Kirstyn and Jack (and Maggie on office duty) since 1998 is a rare thing.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jeff,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>About page, family-owned since 1998 https://tmsdigi.com/about</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2699,23 +2821,28 @@
           <t>Extra design capacity for Go Smart Media</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Hi Tom,
-I saw the piece on your 20 years in business, going back to Cape Breton Web Design in 1999. That's a lot of local businesses helped.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Hey Tom,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Local article on 20 years in business https://capebreton.lokol.me/tom-mills---cape-breton-web-design-seo-and-marketing-consultant</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2793,23 +2920,28 @@
           <t>Extra design capacity for Local SEO Tampa</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>Hi Igor,
-I read your post on designing websites that turn visitors into customers. You clearly treat the site as part of the SEO job, not a separate thing.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Hey Igor,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Blog, designing websites that turn visitors into customers https://localseotampa.com/designing-websites-that-turn-visitors-into-customers-202601/</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2887,23 +3019,28 @@
           <t>White-label web design for Austin Web and Design</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>Hi Isaac,
-I read that you started the company after running marketing at an Austin law firm and seeing how much a good site could do on a sensible budget. That's a very practical reason to start an agency.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Hey Isaac,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>Principals page, Isaac's background before founding in 2009 https://austinwebanddesign.com/about_austin_web_and_design/principals/isaac-simon/</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -2981,23 +3118,28 @@
           <t>Design help for Kansas City Web Design &amp; SEO client sites</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>Hi Phil,
-I came across your Local Business Leaders podcast. Talking to that many owners must give you a clear view of what they actually want from a website.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Hey Phil,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>Local Business Leaders podcast hosted by Phil https://kcwebdesigner.com/local-business-leaders-podcast/</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3079,23 +3221,28 @@
           <t>White-label web design for Lazarus Design Team</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>Hi Brett,
-I noticed Lazarus Charlotte is now Lazarus Design Team. Rebrands like that usually come with a bigger pipeline.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Hey Brett,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>Team page and rebrand to Lazarus Design Team https://lazarusdesignteam.com/about/</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3173,23 +3320,28 @@
           <t>Design help for Big Red Jelly client sites</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>Hi Josh,
-I found the Branding Bros podcast. Three brothers running an agency together since 2017 is a story in itself.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Hey Josh,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>Branding Bros podcast and company history https://bigredjelly.com/resources/podcast/</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3267,23 +3419,28 @@
           <t>White-label web design for Double Up Digital</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>Hi Justin,
-I like that you avoid pre-built themes and build each site around the client. That's how we work on the design side too.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Hey Justin,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>Custom sites with no pre-built themes, team page https://doubleup.digital/team/justin-radomski/</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3361,23 +3518,28 @@
           <t>White-label web design for Michelle Jones Creative</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Hi Michelle,
-I noticed you're clear that work never gets handed to junior staff or offshore teams. That's exactly why a white-label partner has to be senior and invisible.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michelle,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>Home and web design pages, boutique studio, no offshore handoffs https://www.michellejonescreative.com/home</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3455,23 +3617,28 @@
           <t>Extra design capacity for Vincent Design</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>Hi Shaun,
-I noticed your Indigenous web design work. Building sites that carry a community's own voice takes a lot more care than a standard brief.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Hey Shaun,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>Indigenous web design page https://vincentdesign.ca/indigenous-web-design/</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3549,23 +3716,28 @@
           <t>Design help for YEG Digital client sites</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Hi Paul,
-I looked at your Kendal Lighting redesign. Product-heavy sites like that are where the design details really matter.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Hey Paul,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>Case study, Kendal Lighting website redesign https://yegdigital.com/kendal-lighting/</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3643,23 +3815,28 @@
           <t>Extra design capacity for TinyFrog Technologies</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Hi Mikel,
-Congrats on being named a top San Diego web design agency. Growing to around 20 people since 2003 is steady work.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mikel,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>Recognition as a top San Diego web design agency https://tinyfrog.com/top-san-diego-web-design-agency/</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3737,23 +3914,28 @@
           <t>White-label web design for Ignite Web Design &amp; Development</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Hi Aaron,
-I saw you've built a niche in med spa websites. That's a category where the visuals carry most of the sale.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Hey Aaron,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>Medical spa web design page https://ignitewebdesign.ca/medical-spa-web-design</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3831,23 +4013,28 @@
           <t>Design help for Higher Images client sites</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>Hi Linda,
-Congrats on stepping in as President, and on passing 10,000 websites. That's a serious volume of design work to keep consistent.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Hey Linda,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>Press posts, Linda Jo named President and 10,000 websites milestone https://www.higherimages.com/higher-images-surpasses-10000-websites-and-10-million-leads-generated-for-businesses/</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -3925,23 +4112,28 @@
           <t>White-label web design for Pixelstrike Creative</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Hi Juliette,
-I like your Website Master Plan idea. Getting clients to think through the plan before design starts saves everyone a lot of revisions.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Hey Juliette,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>Website Master Plan offer https://pixelstrikecreative.com/masterplan/</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4023,23 +4215,28 @@
           <t>White-label web design for Full Circle Web</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>Hi Danielle,
-Your guide to getting a Google Grant for Canadian charities is really useful. It shows how much you care about the non-profits you build for.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Hey Danielle,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>Blog, steps to get a Google Grant https://fullcircleweb.ca/9-steps-to-get-a-google-grant/</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4117,23 +4314,28 @@
           <t>Extra design capacity for Gravity Junction</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>Hi Sharla,
-I noticed you've built Gravity Junction up since 2009 and serve clients from Atlanta to Grand Rapids. That's a wide spread for one team.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sharla,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>Founder page and web design location pages https://gravityjunction.com/sharla-crawford/</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4211,23 +4413,28 @@
           <t>Extra design capacity for JSL Marketing &amp; Web Design</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>Hi Sarah,
-Your book plus website package for authors is a clever niche. Author sites need a lot of visual personality.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sarah,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>Author book plus website package https://jsl.marketing/author-package/</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4305,23 +4512,28 @@
           <t>Extra design capacity for Garza Web Design</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>Hi Frederico,
-Seventeen years designing sites for Richmond businesses from your Main Street office is a long, steady run.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Hey Frederico,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>About page, founded 2009 https://garzawebdesign.com/about-us</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4399,23 +4611,28 @@
           <t>Design help for The Creative Momentum client sites</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Hi Michael,
-I liked that you publish your own sales team's HubSpot review as a case study. It's rare for an agency to show its own process that openly.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>Blog case study on their HubSpot CRM https://www.thecreativemomentum.com/blog/case-study-the-creative-momentums-sales-team-examines-the-hubspot-crm</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4497,23 +4714,28 @@
           <t>Extra design capacity for Flamingo Agency</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>Hi Chris,
-I read your guide on contact page design for small businesses. It's the page most agencies rush, so it was good to see it get real attention.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>Blog, contact page design best practices https://www.flamingoagency.com/blog/contact-page-design/</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4591,23 +4813,28 @@
           <t>Extra design capacity for 1Brand Design</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>Hi Mike,
-I read your Voyage Chicago interview. Going from creative director roles to running your own shop since 2009 is a path a lot of us know.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mike,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>Voyage Chicago interview with Mike https://1brand.design/blog/mike-kotler-voyage-chicago/</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4685,23 +4912,28 @@
           <t>White-label web design for Sayenko Design</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>Hi Mike,
-I read your piece on UI and UX trends for 2026. It's clear you think about design first, which is rare for a WordPress shop.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mike,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>Blog, UI/UX trends 2026 https://www.sayenkodesign.com/user-experience-trends-2026/</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4783,23 +5015,28 @@
           <t>Design help for Kelly Website Design client sites</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Hi Ed,
-I like that you and Kaitlin keep the agency small and hands-on. Clients can tell when the people they meet are the ones doing the work.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ed,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>About page, small hands-on agency led by Ed Kelly and Kaitlin Farris https://www.kellywebsitedesign.com/about-us/</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4877,23 +5114,28 @@
           <t>White-label web design for My Little Big Web</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>Hi Max,
-I noticed you've got no sales team, people talk straight to you, Eugénie or a project lead. That's a model I respect.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Hey Max,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
         <is>
           <t>Contact page, clients connect directly with the co-founders https://mylittlebigweb.com/en/contact-us/</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -4971,23 +5213,28 @@
           <t>Extra design capacity for ShiftWeb</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>Hi Sinoun,
-I noticed you've made web accessibility part of the core offer. Most agencies still treat it as an afterthought.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Hey Sinoun,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>Services include web accessibility, remote team since 2011 https://shiftweb.com/team/</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5069,23 +5316,28 @@
           <t>Design help for Biondo Creative client sites</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>Hi Anthony,
-Congrats on the Philadelphia Inquirer naming you a favorite web design company. That's a nice local win.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Hey Anthony,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>Press release, Philly Favorites web design company https://www.biondocreative.com/press-releases/2025/philly-favorites-names-biondo-creative-favorite-web-design-company/</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5163,23 +5415,28 @@
           <t>Design help for Bizango client sites</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>Hi Mark,
-I liked your post on the role of branding in web design. A creative writing background clearly shows in how you think about story.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Hey Mark,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>Blog, role of branding in web design https://bizango.com/blog/the-role-of-branding-in-web-design</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5257,23 +5514,28 @@
           <t>Extra design capacity for Matchbox Design Group</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>Hi Brent,
-I came across the Mix and Matchbox podcast. Twenty years in and still putting out content like that says a lot about the team.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Hey Brent,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>Mix and Matchbox podcast page https://matchboxdesigngroup.com/about/mix-matchbox-podcast-digital-marketing/</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5355,23 +5617,28 @@
           <t>Design help for Hiilite client sites</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>Hi William,
-I saw you offer business consulting with William on top of design and SEO. Agencies that coach clients on the business side usually get pulled into bigger site projects.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Hey William,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>Business consulting offer https://hiilite.com/services/business-consulting/</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5449,23 +5716,28 @@
           <t>White-label web design for Circle City Digital</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>Hi Kevin,
-I like that you call yourselves small but mighty and put support front and center. That's usually what keeps clients around for the next redesign.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Hey Kevin,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
         <is>
           <t>About page, small team with dedicated support https://circlecitydigital.com/about/</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5543,23 +5815,28 @@
           <t>Design help for 314media client sites</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>Hi Chris,
-I noticed you lead with strategy-first websites for St. Louis businesses. That's the right order, and it's where good design partners earn their keep.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>Homepage, strategy-first custom websites https://www.314media.com/</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5637,23 +5914,28 @@
           <t>Extra design capacity for Toohill Consulting</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>Hi Andrew,
-I noticed you serve Louisville, Lexington, Nashville, Cincinnati and Chicago. That's a lot of markets for a small owner-led team.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>Hey Andrew,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
         <is>
           <t>City service pages for web design https://toohillconsulting.com/louisville-web-design/</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5731,23 +6013,28 @@
           <t>Design help for Kinex Media client sites</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>Hi Karan,
-I saw you're serving Kelowna as well as the GTA. Running two markets usually means design demand comes in waves.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Hey Karan,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>Kelowna web design page https://www.kinexmedia.com/web-design-kelowna/</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5825,23 +6112,28 @@
           <t>Design help for Be Aligned Web Design client sites</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>Hi Erin,
-West Point to web design and copywriting is not a path I see often. I imagine it shapes how you run projects.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Hey Erin,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
         <is>
           <t>About page, founder background https://www.bealignedwebdesign.com/about</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -5919,23 +6211,28 @@
           <t>White-label web design for ATTRACT Media</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>Hi Ryan,
-I read your post on redesigning a site without losing SEO. That's the question every client with an old site asks first.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ryan,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>Blog, website redesign without losing SEO https://letsattract.com/how-to-do-a-website-redesign-in-saskatoon-without-losing-seo/</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6013,23 +6310,28 @@
           <t>Extra design capacity for Hudson Brauntz Digital</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>Hi David,
-Over 224 sites designed since 2010 is a solid track record for a Cincinnati shop. That's a lot of design hours.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Hey David,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
         <is>
           <t>Homepage, 224+ websites since 2010 https://hudsonbrauntz.com/</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6107,23 +6409,28 @@
           <t>Design help for Hayes Web client sites</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>Hi Curt,
-I noticed you run Hayes Web with two local brand designers working alongside you. Small teams like that are exactly where extra design hands help in busy months.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Hey Curt,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
         <is>
           <t>Company page, boutique studio with two brand designers https://hayesweb.ca/company/</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6201,23 +6508,28 @@
           <t>Design help for REM Web Solutions client sites</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>Hi Rob,
-I read your post on REM's guiding principles. Twenty-five years in, it's good to see a shop that still writes down how it wants to work.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Hey Rob,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>Blog, REM's guiding principles https://www.remwebsolutions.com/blog/rem-s-guiding-principles</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6295,23 +6607,28 @@
           <t>Extra design capacity for Big Creative</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>Hi Chris,
-I saw the move from QT Web Designs to Big Creative. A rename after that many years usually means the work got bigger.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chris,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
         <is>
           <t>Who and what page, rebrand from QT Web Designs https://bigcreative.ca/who-what/</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6393,23 +6710,28 @@
           <t>Design help for Zeal Media client sites</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>Hi Ryan,
-I liked your post on not making the best first impression. It's a good reminder that the website is usually the first handshake.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ryan,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
         <is>
           <t>Blog, not the best first impression https://zealmedia.ca/blog/not-the-best-first-impression/</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6487,23 +6809,28 @@
           <t>White-label web design for Ladybugz Interactive</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>Hi Lysa,
-I read how Ladybugz became a go-to digital partner for early-growth biotechs. That's a demanding niche for design.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Hey Lysa,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
         <is>
           <t>Post on becoming a digital partner for biotechs https://www.ladybugz.com/digital-agency-for-the-future/</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6581,23 +6908,28 @@
           <t>Design help for Rootless Agency client sites</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>Hi Xhulio,
-I read the Rootless back story. Starting in 2021 and already building sites for startups across Massachusetts is quick progress.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Hey Xhulio,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
         <is>
           <t>Blog, Rootless Agency the back story https://rootlessagency.com/rootless-agency-the-back-story/</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6675,23 +7007,28 @@
           <t>Extra design capacity for Web Theory Designs</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>Hi Luis,
-I noticed you've expanded from Houston into Dallas, Austin and San Antonio. Growing across Texas like that puts a lot of pressure on design capacity.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Hey Luis,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
         <is>
           <t>City pages for Dallas, Austin, San Antonio web design https://www.webtheorydesigns.com/dallas-web-design/</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6769,23 +7106,28 @@
           <t>Design help for Big D Creative client sites</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>Hi Curt,
-I looked at your team page, you've got a proper design team lead plus WordPress and SEO people. At that size, a white-label design partner can take overflow without you hiring.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Hey Curt,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>Our team page https://www.bigdcreative.com/our-team/</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6863,23 +7205,28 @@
           <t>Design help for Brandcoders client sites</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Hi Dimitri,
-I looked at your Rooquest case study. Pairing branding and the build under one roof is a strong offer.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Hey Dimitri,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
         <is>
           <t>Case study, Rooquest https://brandcoders.com/case-study/rooquest/</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -6961,23 +7308,28 @@
           <t>Extra design capacity for Vegas Website Designs</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>Hi Marie,
-I like that you and Ryan treat client problems as if they were your own business. That's the kind of shop that keeps clients for years.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Hey Marie,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
         <is>
           <t>About page, founded by Marie and Ryan https://www.vegaswebsitedesigns.com/about/</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7055,23 +7407,28 @@
           <t>Design help for Uptown Studios client sites</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>Hi Tina,
-I read that you started Uptown in your living room in 1992. More than thirty years later with a full crew is a great story.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Hey Tina,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
         <is>
           <t>Tina's staff page and founding story https://uptownstudios.net/staff/tina-reynolds/</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7149,23 +7506,28 @@
           <t>White-label web design for Mvestor Media</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>Hi Ian,
-I liked your post on purpose-driven small business web design. Saying you never use templates is exactly how we work too.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Hey Ian,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
         <is>
           <t>Blog, purpose-driven small business web design https://www.mvestormedia.com/blog/create-purpose-driven-functional-small-business-web-design/</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7247,23 +7609,28 @@
           <t>Extra design capacity for Sacramento Web Design Group</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>Hi TJ,
-I read that you started the group to give Sacramento businesses a cost-effective alternative to the usual agency pricing. A design partner on retainer fits that model well.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Hey TJ,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
         <is>
           <t>About page, founder's reason for starting https://sacramentowebdesigngroup.com/about/</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7345,23 +7712,28 @@
           <t>Extra design capacity for Web Design Sacramento (Kova Team)</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>Hi David,
-I saw the press piece on Web Design Sacramento and the tailored solutions you offer local businesses. Being the local partner is a strong position.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Hey David,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
         <is>
           <t>Press release, May 2025 https://www.financialcontent.com/article/marketersmedia-2025-5-19-web-design-sacramento-by-kova-team-offers-tailored-digital-solutions-for-sacramento-businesses</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7439,23 +7811,28 @@
           <t>White-label web design for BDX Omaha (Beardman Design)</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>Hi Tyson,
-I like that you've kept BDX small on purpose so the person selling the plan is the one building it. A white-label design partner fits that model without adding headcount.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Hey Tyson,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
         <is>
           <t>About page, founder-led small senior team https://beardmandesign.com/about/</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7533,23 +7910,28 @@
           <t>White-label web design for LGX Branding (little guy branding)</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>Hi Matt,
-I read your origin story post about going from little guy design to lgx. Rebrands like that usually mean the work outgrew the old name.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Hey Matt,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
         <is>
           <t>Blog, rebrand from LGD to lgx https://www.lgxbranding.com/weve-rebranded-from-lgd-to-lgx-our-origin-story/</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7631,23 +8013,28 @@
           <t>White-label web design for Team 218 Web Services</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>Hi Chuck,
-No deposits and twelve months of care is a bold offer. It tells me you're confident in the sites you ship.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Hey Chuck,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
         <is>
           <t>Service area page, no deposits and 12 months care https://team218.com/service-areas/des-moines/</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -7713,23 +8100,28 @@
           <t>Design help for Interactive Builds client sites</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>Hi Interactive Builds team,
-I noticed you've built a niche in websites for accountants and CPA firms. Security plus trust signals is a tricky design brief to get right.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Hey Interactive Builds team,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
         <is>
           <t>Web design for accountants page https://www.interactivebuilds.com/web-design-for-accountants/</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>needs_check: no named decision-maker found</t>
         </is>
@@ -7799,23 +8191,28 @@
           <t>Extra design capacity for Shift8 Web</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>Hi Suzanne,
-I liked the line on your site about every build being custom and not a template with swapped colours. We work the same way.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Hey Suzanne,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
         <is>
           <t>Homepage, custom builds not templates https://shift8web.ca/</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>needs_check: no published email and no Icypeas-confirmed address</t>
         </is>
@@ -7885,23 +8282,28 @@
           <t>Extra design capacity for Redwood Productions</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>Hi Jennifer,
-Congrats on the move into the new office in Wake Forest. That usually means the work is growing.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jennifer,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
         <is>
           <t>Blog post, new office announcement https://redwoodproductions.com/were-in-our-new-office/</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>needs_check: no published email and no Icypeas-confirmed address</t>
         </is>
@@ -7967,23 +8369,28 @@
           <t>White-label web design for Thought Media</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>Hi Thought Media team,
-I noticed you've got a 16 person core team split across Toronto and New York. That's the size where design capacity starts to get tight in busy months.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Hey Thought Media team,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
         <is>
           <t>Meet the team page, 16 person core team https://thoughtmedia.ca/about-us/</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>needs_check: no named decision-maker found</t>
         </is>
@@ -8049,23 +8456,28 @@
           <t>Design help for Web Workshop client sites</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>Hi Web Workshop team,
-I noticed you focus on startups and ecommerce brands and handle both the identity and the site. That kind of end-to-end work gets heavy on design time.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Open to a quick look at some recent work? I can send a few Figma files over, no call needed.
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Hey Web Workshop team,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
         <is>
           <t>About page, branding and web design for startups and ecommerce https://webworkshop.ca/about/</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>needs_check: no named decision-maker found</t>
         </is>
@@ -8135,23 +8547,28 @@
           <t>Design help for Ohio Web Agency client sites</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>Hi Jason,
-I like how you package web design, SEO and reputation work into one strategic campaign. The site ends up being the centerpiece of all of it.
-I'm Darjan from evie.design. We work behind the scenes for agencies, designing custom websites that go out under your brand. You get organized Figma files and your developers take it from there. Everything is designed from scratch, no themes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>Hey Jason,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
         <is>
           <t>About page, all-inclusive web campaign offer https://www.ohiowebagency.com/about-us/</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>needs_check: no published email and no Icypeas-confirmed address</t>
         </is>
@@ -8221,23 +8638,28 @@
           <t>Design help for Bespoke Web Design client sites</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>Hi Charles,
-I read that you taught yourself web design as a stay-at-home dad and built Bespoke around trades businesses. Picking a niche like that early pays off.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-Would it help if I sent a couple of recent Figma files so you can see what your developers would get?
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>Hey Charles,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
         <is>
           <t>About page, founder story and focus on trades https://bespokewebdesign.ca/about/</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>needs_check: no published email and no Icypeas-confirmed address</t>
         </is>
@@ -8307,23 +8729,28 @@
           <t>Extra design capacity for Emerge</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>Hi Adam,
-The Sanford Insurance case study stood out, 775 new users in a year for a local insurance agency is a real result.
-Quick intro, I'm Darjan and I run evie.design. Agencies bring us in as their white-label design team. We design the site in Figma, fully custom, and your devs build it. We don't do development, so we never step on your team's toes.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Hey Adam,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
         <is>
           <t>Case study, Sanford Insurance https://emergerichmond.com/project/in-one-year-775-new-users-found-richmonds-own-sanford-insurance/</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>needs_check: no published email and no Icypeas-confirmed address</t>
         </is>
@@ -8393,23 +8820,28 @@
           <t>Design help for Lynk Web Design &amp; Marketing client sites</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>Hi Loretta,
-I read that you still manage client projects yourself while running Lynk day to day. That hands-on approach usually means design time is the first thing to get squeezed.
-I run evie.design. We're a white-label design partner for agencies, so we design fully custom websites under your name and hand over clean Figma files your own developers build from. No templates, and we stay out of development entirely.
-Most partners use a monthly retainer with no long-term contract, which works out cheaper per task than paying one-off. If you'd rather go project by project, that works too.
-If extra design capacity would be useful this quarter, happy to send a few examples your way.
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>Hey Loretta,
+[OPENING LINE MISSING, write one sentence about their work]
+That's actually why I'm emailing. I run evie.design, a white label partner for agencies. Design only, no dev, and everything's made to match your client's brand rather than pulled from a template. You get clean Figma files your team can build straight from. Your client never even knows we exist, it's all under your name.
+Some agencies bring me in just for the overflow weeks. Some keep me running alongside their own designer so nobody's drowning. A few just let me handle design entirely so they're not stuck hiring for it. Whatever setup works for you, I'll fit into it.
+I've been doing this for years now. Here's what Chris Castillo, SEO Specialist and CEO of PDMS, had to say after a few years of working together.
+"Darjan makes my job so much easier, five years in and we're still working with him. He knows our clients, our voice, our standards, and his attention to detail is exactly why we keep coming back. Our clients' results have noticeably improved with the conversion-focused work he produces."
+If it's worth 20 minutes, [grab a slot here](https://cal.com/evie.design/20min), or just hit reply and we'll figure out a time.
+Cheers,
 Darjan
-evie.design</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
+P.S. You can see my work [here](https://evie.design)</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
         <is>
           <t>Vancouver Island page, founder still manages projects https://lynkwebsitedesign.com/web-design-vancouver-island</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>needs_check: no published email and no Icypeas-confirmed address</t>
         </is>
@@ -8451,13 +8883,15 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
         <is>
           <t>https://www.gasmandesign.com/about/</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>skip: solo freelancer (founder describes himself as a freelance website designer)</t>
         </is>
@@ -8499,13 +8933,15 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
         <is>
           <t>https://www.brightsidekc.com/about</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>skip: two-person studio (Katie and Jess), well under 5 people</t>
         </is>
@@ -8547,13 +8983,15 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
         <is>
           <t>https://www.objective.dev/about/</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>skip: primarily a software and app development shop</t>
         </is>
@@ -8595,13 +9033,15 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
         <is>
           <t>https://www.roketco.com/</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>skip: primarily an app design and development agency</t>
         </is>
@@ -8643,13 +9083,15 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
         <is>
           <t>https://www.goldenlaunchcreative.com/shop-templates/charlene-squarespace-template</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>skip: sells Squarespace templates alongside services, and appears founder-only</t>
         </is>
@@ -8691,13 +9133,15 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" s="2" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
         <is>
           <t>https://louisvillewebnerds.com/about/</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>skip: appears to be a solo operator (Cody Wheeler)</t>
         </is>
@@ -8739,13 +9183,15 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
         <is>
           <t>https://kdesign.co/</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>skip: solo designer</t>
         </is>
@@ -8787,13 +9233,15 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
         <is>
           <t>https://www.wisegrowthmarketing.com/service/free-website-diy/</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>skip: sells Wix and free DIY template websites</t>
         </is>
@@ -8835,13 +9283,15 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
         <is>
           <t>https://www.dallaswebagency.us/</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>skip: is itself a white-label web agency (competitor, not a prospect)</t>
         </is>
@@ -8883,13 +9333,15 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
         <is>
           <t>https://m5designstudio.com/services/</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>skip: about 3 employees and markets WordPress templates</t>
         </is>

--- a/lead_research/leads.xlsx
+++ b/lead_research/leads.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R230"/>
+  <dimension ref="A1:S230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -437,10 +437,11 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,20 +517,25 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>angle</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>opening_line</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>opening_source_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>research_note</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -602,14 +608,15 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Blog post on SEO and AI search for Boise businesses https://idahowebsites.com/the-boise-business-guide-to-seo-ai-search-how-to-get-your-site-found-by-chatgpt-gemini/</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -682,14 +689,15 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Blog post on content writing in web design https://www.tagteamdesign.com/content-writing-in-web-design-building-a-website-that-tells-your-brands-story/</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -762,14 +770,15 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Case study, 10x ROI with Google Ads https://cornerstone.studio/10x-roi-google-ads/</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -842,14 +851,15 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>About page, studio for founders with hubs in Portland and Denver https://perspektiiv.com/aboutperspektiiv</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -922,14 +932,15 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Packaging design and branding page https://jyzdesign.com/packaging-design/</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1002,14 +1013,15 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Adam's team bio, former touring and session drummer https://muletowndigital.com/about/team/adam-silverman/</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1082,14 +1094,15 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Blog, 10 Best Therapist Website Designs of 2026 https://azurodigital.com/therapist-website-examples/</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1162,14 +1175,15 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>Founder page, built and sold a construction company at 21 https://marvelmarketing.ca/ryan-mcrae/</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1242,14 +1256,15 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Video marketing plus website design categories on their blog https://www.redfoxvisual.com/category/video-marketing/</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1322,14 +1337,15 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Homepage, small team with low overhead and competitive pricing https://www.lifewebanddesign.com/</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1402,14 +1418,15 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>Colorado web design blog and town pages https://bullfinch.io/blog/colorado-web-design/</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1482,14 +1499,15 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>Article, the dental website that converts new patients https://justbydesign.com/seo-ai-marketing-resources/digital-strategy-marketing/dental-website-that-converts/</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1562,14 +1580,15 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>About page, founded 2010, custom web design in Boise https://www.thrivewebdesigns.com/about/</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1642,14 +1661,15 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>Page-in-a-Day website offer https://www.lakedesignmn.com/page-in-a-day-website</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1722,14 +1742,15 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>Unlimited WordPress support offer https://themightymo.com/unlimited-wordpress-support/</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1802,14 +1823,15 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>Blog, the story behind the Webconsuls name https://www.webconsuls.com/blog/2019/05/webconsuls-business-name/</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1882,14 +1904,15 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>Homepage, 2026 Webby Award winner https://chariotcreative.com/</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -1962,14 +1985,15 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>Blog, designing websites that turn visitors into customers https://localseotampa.com/designing-websites-that-turn-visitors-into-customers-202601/</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2042,14 +2066,15 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>Principals page, Isaac's background before founding in 2009 https://austinwebanddesign.com/about_austin_web_and_design/principals/isaac-simon/</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2122,14 +2147,15 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>Local Business Leaders podcast hosted by Phil https://kcwebdesigner.com/local-business-leaders-podcast/</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2202,14 +2228,15 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>Branding Bros podcast and company history https://bigredjelly.com/resources/podcast/</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2282,14 +2309,15 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>Custom sites with no pre-built themes, team page https://doubleup.digital/team/justin-radomski/</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2362,14 +2390,15 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>Home and web design pages, boutique studio, no offshore handoffs https://www.michellejonescreative.com/home</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2442,14 +2471,15 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>Indigenous web design page https://vincentdesign.ca/indigenous-web-design/</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2522,14 +2552,15 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>Case study, Kendal Lighting website redesign https://yegdigital.com/kendal-lighting/</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2602,14 +2633,15 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>Recognition as a top San Diego web design agency https://tinyfrog.com/top-san-diego-web-design-agency/</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2682,14 +2714,15 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>Medical spa web design page https://ignitewebdesign.ca/medical-spa-web-design</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2762,14 +2795,15 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>Press posts, Linda Jo named President and 10,000 websites milestone https://www.higherimages.com/higher-images-surpasses-10000-websites-and-10-million-leads-generated-for-businesses/</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2842,14 +2876,15 @@
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>Website Master Plan offer https://pixelstrikecreative.com/masterplan/</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -2922,14 +2957,15 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>Founder page and web design location pages https://gravityjunction.com/sharla-crawford/</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3002,14 +3038,15 @@
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>Author book plus website package https://jsl.marketing/author-package/</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3082,14 +3119,15 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>About page, founded 2009 https://garzawebdesign.com/about-us</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3162,14 +3200,15 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>Blog case study on their HubSpot CRM https://www.thecreativemomentum.com/blog/case-study-the-creative-momentums-sales-team-examines-the-hubspot-crm</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3242,14 +3281,15 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>Voyage Chicago interview with Mike https://1brand.design/blog/mike-kotler-voyage-chicago/</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3322,14 +3362,15 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>Blog, UI/UX trends 2026 https://www.sayenkodesign.com/user-experience-trends-2026/</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3402,14 +3443,15 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>Contact page, clients connect directly with the co-founders https://mylittlebigweb.com/en/contact-us/</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3482,14 +3524,15 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>Services include web accessibility, remote team since 2011 https://shiftweb.com/team/</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3562,14 +3605,15 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>Blog, role of branding in web design https://bizango.com/blog/the-role-of-branding-in-web-design</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3642,14 +3686,15 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>Mix and Matchbox podcast page https://matchboxdesigngroup.com/about/mix-matchbox-podcast-digital-marketing/</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3722,14 +3767,15 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>About page, small team with dedicated support https://circlecitydigital.com/about/</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3802,14 +3848,15 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>Homepage, strategy-first custom websites https://www.314media.com/</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3882,14 +3929,15 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>City service pages for web design https://toohillconsulting.com/louisville-web-design/</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -3962,14 +4010,15 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>Kelowna web design page https://www.kinexmedia.com/web-design-kelowna/</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4042,14 +4091,15 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>About page, founder background https://www.bealignedwebdesign.com/about</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4122,14 +4172,15 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>Blog, website redesign without losing SEO https://letsattract.com/how-to-do-a-website-redesign-in-saskatoon-without-losing-seo/</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4202,14 +4253,15 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>Homepage, 224+ websites since 2010 https://hudsonbrauntz.com/</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4282,14 +4334,15 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>Company page, boutique studio with two brand designers https://hayesweb.ca/company/</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4362,14 +4415,15 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>Blog, REM's guiding principles https://www.remwebsolutions.com/blog/rem-s-guiding-principles</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4442,14 +4496,15 @@
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>Who and what page, rebrand from QT Web Designs https://bigcreative.ca/who-what/</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4522,14 +4577,15 @@
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>Post on becoming a digital partner for biotechs https://www.ladybugz.com/digital-agency-for-the-future/</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4602,14 +4658,15 @@
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>Blog, Rootless Agency the back story https://rootlessagency.com/rootless-agency-the-back-story/</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4682,14 +4739,15 @@
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>City pages for Dallas, Austin, San Antonio web design https://www.webtheorydesigns.com/dallas-web-design/</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4762,14 +4820,15 @@
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>Our team page https://www.bigdcreative.com/our-team/</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4842,14 +4901,15 @@
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>Case study, Rooquest https://brandcoders.com/case-study/rooquest/</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -4922,14 +4982,15 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>Tina's staff page and founding story https://uptownstudios.net/staff/tina-reynolds/</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5002,14 +5063,15 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>Blog, purpose-driven small business web design https://www.mvestormedia.com/blog/create-purpose-driven-functional-small-business-web-design/</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5082,14 +5144,15 @@
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>About page, founder-led small senior team https://beardmandesign.com/about/</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5162,14 +5225,15 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>Blog, rebrand from LGD to lgx https://www.lgxbranding.com/weve-rebranded-from-lgd-to-lgx-our-origin-story/</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5242,14 +5306,15 @@
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>About page, relaunched as Brad's founder-led studio https://www.omahamediagroup.com/about</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5322,14 +5387,15 @@
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>Site OnCall CMS in the main navigation https://visionary.com/; general address a general address replaced by Icypeas-confirmed bryan@visionary.com</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5402,14 +5468,15 @@
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>Krew page on performance and creative sharing a brief https://kreative-media.com/krew/</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5482,14 +5549,15 @@
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>Homepage, 'every project begins with strategy, not design' https://www.webloftdesigns.com/ . Only the first name Marina is published.</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5562,14 +5630,15 @@
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>Homepage special sale, all-in-one package $2490 https://blesswebdesigns.com/; general address a general address replaced by Icypeas-confirmed nibin@blesswebdesigns.com</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5642,14 +5711,15 @@
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" s="2" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
         <is>
           <t>Blog post on moving into Oak Park https://www.wearescribe.com/notes/welcome-to-the-scribe-neighborhood/ . The site names Alli, the surname and co-founder title come from search results (LinkedIn company page).; general address a general address replaced by Icypeas-confirmed alli@wearescribe.com</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5722,14 +5792,15 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
         <is>
           <t>About page on long retainers https://velocitymedialab.com/about/</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5802,14 +5873,15 @@
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
         <is>
           <t>Homepage quote 'Fortune Favors the Fearless. BEN CAPA, CEO' and Shopify partner line https://fudogmedia.net/ . ben@fudogarmy.com is published on the agency's own privacy policy page (fudogarmy.com is their second domain).</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5882,14 +5954,15 @@
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
         <is>
           <t>Team page, Amir Vincent Co-Founder &amp; CEO, Sam Vincent Co-Founder &amp; Art Director https://canadacreate.com/team/; general address a general address replaced by Icypeas-confirmed amir@canadacreate.com</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -5962,14 +6035,15 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
         <is>
           <t>Meet the team, Rob Balla bio, 25 years as creative director https://www.ballamedia.ca/meet-the-team; general address amazingservice@ballamedia.ca replaced by Icypeas-confirmed rob@ballamedia.ca</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6042,14 +6116,15 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
         <is>
           <t>About page, Our Story, partners Sandro and Adwin https://stiganmedia.com/about/ . Only first names are published.; general address a general address replaced by Icypeas-confirmed sandro@stiganmedia.com</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6122,14 +6197,15 @@
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>About page, Indigenous owned agency verified through the Canadian Council for Indigenous Business, building a team while preserving the personal experience https://leannedigital.com/about/</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6202,14 +6278,15 @@
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
         <is>
           <t>Services menu, website design plus print and branding https://littledragon.ca/ ; founder on About page https://littledragon.ca/about/; general address a general address replaced by Icypeas-confirmed amine@littledragon.ca</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6282,14 +6359,15 @@
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
         <is>
           <t>About page, Awwwards nominee and team with Cezar as CEO https://dasweb.ca/about-dasweb/ . Only first names are published.</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6362,14 +6440,15 @@
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
         <is>
           <t>Homepage, Pillars of Partnership and a testimonial from a marketing director across 3 brands over 15 years https://www.seoteric.com/; general address a general address replaced by Icypeas-confirmed matt@seoteric.com</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6442,14 +6521,15 @@
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
         <is>
           <t>Industry verticals from the site and search results https://southerndigitalconsulting.com/ . Name and address from the terms of service page; co-founder title from https://www.crunchbase.com/person/nick-rizkalla (search result).</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6522,14 +6602,15 @@
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
         <is>
           <t>About page, 6 full-time team members, 80-ish active clients, founded 2020 https://www.launchkitdesign.com/about-us</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6602,14 +6683,15 @@
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
         <is>
           <t>About page, team description and Team Leaders https://mindspikedesign.com/about/</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6682,14 +6764,15 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
         <is>
           <t>Homepage, Milwaukee Brewers project and service list https://revpop.com/</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6762,14 +6845,15 @@
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
         <is>
           <t>Homepage, 'Owner-level strategy before design starts' https://brewcitymarketing.com/; general address a general address replaced by Icypeas-confirmed amanda@brewcitymarketing.com</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6842,14 +6926,15 @@
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
         <is>
           <t>Homepage, longest client relationship 13 years and counting https://milwaukee-webdesigner.com/</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -6922,14 +7007,15 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
         <is>
           <t>Web design service page, hundreds of WordPress sites managed https://jackandbean.com/service/web-design-tucson-az/; general address grow@jackandbean.com replaced by Icypeas-confirmed jack@jackandbean.com</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7002,14 +7088,15 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
         <is>
           <t>About page key facts (founded 2006, founder Eric Caldwell, own mini-CMS) and client review mentioning 24 years https://www.web-jive.com/about-web-jive/; general address a general address replaced by Icypeas-confirmed eric@web-jive.com</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7082,14 +7169,15 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" s="2" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
         <is>
           <t>Homepage and about page team, Tim Hendry Founder Visionary and Andre Anderson Founder Integrator https://www.modiphy.com/about</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7162,14 +7250,15 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
         <is>
           <t>About page, Our Story, started in 1999 by Alli Summerford https://dandelionmarketing.com/about-dandelion/</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7242,14 +7331,15 @@
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
         <is>
           <t>Staff page, 'Small But Mighty Team' https://leemediagroup.com/staff/; general address a general address replaced by Icypeas-confirmed mia@leemediagroup.com</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7322,14 +7412,15 @@
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
         <is>
           <t>Meet the Team page, photographers and videographers https://www.visualmediagroupllc.com/about/team/ . a general address is published on their own privacy page.; general address a general address replaced by Icypeas-confirmed lindon@visualmediagroupllc.com</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7402,14 +7493,15 @@
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
         <is>
           <t>Our Story page, 2008 Humble Beginnings, Daniel Bell founder https://newbird.com/our-story/; general address a general address replaced by Icypeas-confirmed dbell@newbird.com</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7482,14 +7574,15 @@
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
         <is>
           <t>City service pages for Buffalo and Syracuse https://digitaltheory.studio/buffalo-web-design ; team page https://digitaltheory.studio/our-team; general address hi@digitaltheory.studio replaced by Icypeas-confirmed vietnguyen@digitaltheory.studio</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7562,14 +7655,15 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
         <is>
           <t>About page, Union Wharf location and history since 2002 https://slickfish.com/about-maine-web-design; general address ask@slickfish.com replaced by Icypeas-confirmed gordon@slickfish.com</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7642,14 +7736,15 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
         <is>
           <t>About page, How it started https://blackdoorcreative.com/about/</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7722,14 +7817,15 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
         <is>
           <t>Homepage history since 2010 https://jpgdesigns.com/ ; team page https://jpgdesigns.com/the-jpg-team/</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7802,14 +7898,15 @@
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
         <is>
           <t>About page, company started as owner John Wilson's idea almost 20 years ago, Fulton Savings Bank testimonial https://acs-web.com/about-us; general address a general address replaced by Icypeas-confirmed john@acs-web.com</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7882,14 +7979,15 @@
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
         <is>
           <t>About page, bonus pay, commission and eventual partnership track https://breakthroughdesign.com/about/; general address a general address replaced by Icypeas-confirmed tison@breakthroughdesign.com</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -7962,14 +8060,15 @@
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
         <is>
           <t>About page service areas (Canada, United States, Bermuda) and message from the founder https://www.marketingblendz.com/about/; general address a general address replaced by Icypeas-confirmed filip@marketingblendz.com</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8042,14 +8141,15 @@
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
         <is>
           <t>Homepage, Design Team Downtown Victoria crew and hiring notice https://www.bonecreative.com/; general address a general address replaced by Icypeas-confirmed shon@bonecreative.com</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8122,14 +8222,15 @@
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
         <is>
           <t>About page, Kris OWNER week breakdown (51% running the show, 5% herding cats) https://www.krischislett.com/about-us/</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8202,14 +8303,15 @@
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr">
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
         <is>
           <t>Blog post 'Your Customers are Better Spokespeople Than You' https://propagandacreative.com/your-customers-are-better-spokespeople-than-you/; general address a general address replaced by Icypeas-confirmed jason@propagandacreative.com</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8282,14 +8384,15 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
         <is>
           <t>About page intro and team https://kineticmc.com/about/; general address a general address replaced by Icypeas-confirmed dana@kineticmc.com</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8362,14 +8465,15 @@
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
         <is>
           <t>About page, ag and D2C meat marketing https://www.proofmarketing.com/about</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8442,14 +8546,15 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
         <is>
           <t>About page, woman-owned since 1996 https://www.thegeckoagency.com/about/ . melissa.kaplan@geckodesigns.com is published on their careers page (geckodesigns.com is the agency's older domain).</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8522,14 +8627,15 @@
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr">
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
         <is>
           <t>Meet the Team page, started as a two-person operation with siblings Jason and Stefanie https://www.themediacaptain.com/meet-the-team/; general address a general address replaced by Icypeas-confirmed jason@themediacaptain.com</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8602,14 +8708,15 @@
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr">
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
         <is>
           <t>Testimonials page, 'The owners always respond immediately' https://www.robintek.com/about-us/testimonials/; general address a general address replaced by Icypeas-confirmed jeremy@robintek.com</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8682,14 +8789,15 @@
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr">
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
         <is>
           <t>Team page, Jason R Owner &amp; Lead Designer, sole owner for over 20 years https://redxwebdesign.com/about/our-team . Only the surname initial is published.</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8762,14 +8870,15 @@
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
         <is>
           <t>Awards page, Steve Wolgemuth (CEO) Small Business Person award https://www.ydop.com/about-us/awards/</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8842,14 +8951,15 @@
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr">
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
         <is>
           <t>About page, Jon sets the vision for red K &amp; ReviewUp https://www.redk.co/about-us; general address a general address replaced by Icypeas-confirmed jon@redk.co</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -8922,14 +9032,15 @@
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr">
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
         <is>
           <t>London website design page, one-on-one consultations https://www.branchmarketing.ca/london-website-design . a general address is published on their homepage.; general address a general address replaced by Icypeas-confirmed kerig@branchmarketing.ca</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9002,14 +9113,15 @@
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr">
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
         <is>
           <t>About page, 'We are your digital marketing bench strength' https://momentum360.ca/about/; general address a general address replaced by Icypeas-confirmed ryan@momentum360.ca</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9082,14 +9194,15 @@
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr">
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
         <is>
           <t>San Antonio web design page, end-to-end service with training, hosting and maintenance https://pearanalytics.com/san-antonio-web-design/; general address a general address replaced by Icypeas-confirmed ryan@pearanalytics.com</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="S108" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9162,14 +9275,15 @@
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr">
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
         <is>
           <t>About page, Meet the Team with Paul and Sarah Harkleroad, co-founders https://daordesign.com/about/; general address a general address replaced by Icypeas-confirmed sarah@daordesign.com</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9242,14 +9356,15 @@
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr">
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
         <is>
           <t>Homepage and small business website page, 20+ years, custom explainer videos https://kldesign.com/</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9322,14 +9437,15 @@
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr">
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
         <is>
           <t>About page, woman-owned, small team, clients want someone to take ownership https://meetbonfire.com/about</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9402,14 +9518,15 @@
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr">
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
         <is>
           <t>About page, Chris White owner, 20+ years https://ashevillewebdesign.com/about; general address a general address replaced by Icypeas-confirmed chris@ashevillewebdesign.com</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr">
+      <c r="S112" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9482,14 +9599,15 @@
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr">
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
         <is>
           <t>About page, A Note From Our Founder and 'Our team works closely with leadership' https://www.perfectafternoon.com/about-us/ . The site only lists accounting@ and legal@ addresses, so no outreach address was used.</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="S113" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9562,14 +9680,15 @@
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr">
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
         <is>
           <t>About page, 'Only started on a dare!' in 2008 https://chavezwebdesign.com/about-us-chavez-web-design-noemi-chavez-luis-chavez/</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9642,14 +9761,15 @@
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" s="2" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr">
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
         <is>
           <t>About page, team description https://www.trifectaky.com/about/; general address a general address replaced by Icypeas-confirmed kevin@trifectaky.com</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr">
+      <c r="S115" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9722,14 +9842,15 @@
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr">
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
         <is>
           <t>About the owner page, owner's philosophy https://startupproduction.com/about-the-owner-startup-production/</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="S116" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9802,14 +9923,15 @@
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr">
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
         <is>
           <t>About page, human touch and About the Founder https://www.clickfaktory.com/about/; general address a general address replaced by Icypeas-confirmed phil@clickfaktory.com</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="S117" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9882,14 +10004,15 @@
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr">
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
         <is>
           <t>Homepage and about page, 'A small team with big ambitions' and the sausage factory line https://treize.pro/en/about/</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="S118" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -9962,14 +10085,15 @@
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
-      <c r="O119" s="2" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr">
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
         <is>
           <t>Blog post 'What 400 customer reviews reveal' https://www.redspotdesign.com/what-400-customer-reviews-reveal-about-choosing-a-web-design-company/; general address a general address replaced by Icypeas-confirmed david@redspotdesign.com</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="S119" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10042,14 +10166,15 @@
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" s="2" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr">
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
         <is>
           <t>About page, team and Madison and Milwaukee offices https://accentgraphix.com/about-us/</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr">
+      <c r="S120" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10122,14 +10247,15 @@
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" s="2" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr">
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
         <is>
           <t>Team page, Colleen founded Madison Web Works in 2006 https://www.madisonwebworks.com/team</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10202,14 +10328,15 @@
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr">
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
         <is>
           <t>Who We Are page, team motto and Brent Kogan bio https://www.barrieweb.com/who-we-are/</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr">
+      <c r="S122" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10282,14 +10409,15 @@
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" s="2" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr">
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
         <is>
           <t>Team page, Felix Figuereo Chief Dude, Founder &amp; Managing Director, and trade association work https://nicasiodesign.com/our-team/</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
+      <c r="S123" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10362,14 +10490,15 @@
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr">
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
         <is>
           <t>Homepage, Ted Anderson background as freelancer, corporate graphic artist and webmaster, and agency owner https://www.interactiondevelopers.com/; general address a general address replaced by Icypeas-confirmed tanderson@interactiondevelopers.com</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="S124" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10442,14 +10571,15 @@
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" s="2" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr">
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
         <is>
           <t>About page, 26 years, and services menu with local support and free premium plugins https://www.back40webdesign.com/about-us/ . a general address is published on their homepage.; general address a general address replaced by Icypeas-confirmed dave@back40webdesign.com</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="S125" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10522,14 +10652,15 @@
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr">
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
         <is>
           <t>About page, Our People and open Art Director role https://stridecreative.com/about-us/; general address a general address replaced by Icypeas-confirmed terri@stridecreative.com</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="S126" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10602,14 +10733,15 @@
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
-      <c r="O127" s="2" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr">
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
         <is>
           <t>About page, founder Mike Lannen formed Eternity in his dorm room, 25 years of teamwork https://eternitymarketing.com/about/</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="S127" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10682,14 +10814,15 @@
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr">
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
         <is>
           <t>About page, team selected per client https://www.clovercreativegroup.com/about</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="S128" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10762,14 +10895,15 @@
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" s="2" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr">
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
         <is>
           <t>About page, Meet the Founders, 'two co-founders who remain directly involved' https://exaltodesign.com/about_us/</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10842,14 +10976,15 @@
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" s="2" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr">
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
         <is>
           <t>About page, Cody Chief Canine Officer and Castle &amp; Cooke Hawai'i testimonial https://www.teamvision.com/about-us/; general address a general address replaced by Icypeas-confirmed craig@teamvision.com</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="S130" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -10922,14 +11057,15 @@
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" s="2" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr">
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr">
         <is>
           <t>About page, Meet the LaunchUX Fleet and common sense approach https://launchux.com/about; general address a general address replaced by Icypeas-confirmed nneil@launchux.com</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
+      <c r="S131" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -11002,14 +11138,15 @@
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" s="2" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr">
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
         <is>
           <t>Team page, full ownership and fixed pricing, Jeff Paulson Owner / Full stack developer https://kwdmarketing.ca/team/; general address a general address replaced by Icypeas-confirmed jeff@kwdmarketing.ca</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="S132" t="inlineStr">
         <is>
           <t>missing: opening line</t>
         </is>
@@ -11074,14 +11211,15 @@
           <t>rejected by Icypeas: matt@espysolutions.com, matt.espy@espysolutions.com, mattespy@espysolutions.com, mespy@espysolutions.com, m.espy@espysolutions.com</t>
         </is>
       </c>
-      <c r="O133" s="2" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr">
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr">
         <is>
           <t>Case study, Colorado Adventure Guides https://espysolutions.com/web-design-case-studies/colorado-adventure-guides/</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr">
+      <c r="S133" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11130,14 +11268,15 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr">
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
         <is>
           <t>Web design for accountants page https://www.interactivebuilds.com/web-design-for-accountants/</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="S134" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -11202,14 +11341,15 @@
           <t>rejected by Icypeas: bethany@bethanyworks.com, bethany.mccamish@bethanyworks.com, bethanymccamish@bethanyworks.com, bmccamish@bethanyworks.com, b.mccamish@bethanyworks.com</t>
         </is>
       </c>
-      <c r="O135" s="2" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr">
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
         <is>
           <t>Brandcend, bespoke brand evolution offer https://bethanyworks.com/brandcend/</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
+      <c r="S135" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11274,14 +11414,15 @@
           <t>rejected by Icypeas: suzanne@shift8web.ca, suzanne.thompson@shift8web.ca, suzannethompson@shift8web.ca, sthompson@shift8web.ca, s.thompson@shift8web.ca</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr">
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
         <is>
           <t>Homepage, custom builds not templates https://shift8web.ca/</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="S136" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11346,14 +11487,15 @@
           <t>rejected by Icypeas: lucia@ideamarketing.ca, lucia.siplakova@ideamarketing.ca, luciasiplakova@ideamarketing.ca, lsiplakova@ideamarketing.ca, l.siplakova@ideamarketing.ca</t>
         </is>
       </c>
-      <c r="O137" s="2" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr">
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
         <is>
           <t>VIP Design Day offer https://ideamarketing.ca/vip-design-day/</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="S137" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11418,14 +11560,15 @@
           <t>rejected by Icypeas: jennifer@redwoodproductions.com, jennifer.ray@redwoodproductions.com, jenniferray@redwoodproductions.com, jray@redwoodproductions.com, j.ray@redwoodproductions.com</t>
         </is>
       </c>
-      <c r="O138" s="2" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr">
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
         <is>
           <t>Blog post, new office announcement https://redwoodproductions.com/were-in-our-new-office/</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
+      <c r="S138" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11490,14 +11633,15 @@
           <t>rejected by Icypeas: paul@generatedesign.com, paul.barth@generatedesign.com, paulbarth@generatedesign.com, pbarth@generatedesign.com, p.barth@generatedesign.com</t>
         </is>
       </c>
-      <c r="O139" s="2" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr">
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
         <is>
           <t>How it all started page https://generatedesign.com/design-agency-raleigh/</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
+      <c r="S139" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11562,14 +11706,15 @@
           <t>rejected by Icypeas: jeff@tmsdigi.com, jeff.hayes@tmsdigi.com, jeffhayes@tmsdigi.com, jhayes@tmsdigi.com, j.hayes@tmsdigi.com</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr">
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
         <is>
           <t>About page, family-owned since 1998 https://tmsdigi.com/about</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
+      <c r="S140" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11618,14 +11763,15 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
-      <c r="O141" s="2" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr">
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
         <is>
           <t>Meet the team page, 16 person core team https://thoughtmedia.ca/about-us/</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
+      <c r="S141" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -11690,14 +11836,15 @@
           <t>rejected by Icypeas: tom@gosmartmedia.com, tom.mills@gosmartmedia.com, tommills@gosmartmedia.com, tmills@gosmartmedia.com, t.mills@gosmartmedia.com</t>
         </is>
       </c>
-      <c r="O142" s="2" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr">
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
         <is>
           <t>Local article on 20 years in business https://capebreton.lokol.me/tom-mills---cape-breton-web-design-seo-and-marketing-consultant</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
+      <c r="S142" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11762,14 +11909,15 @@
           <t>rejected by Icypeas: brett@lazaruscharlotte.com, brett.honerkamp@lazaruscharlotte.com, bretthonerkamp@lazaruscharlotte.com, bhonerkamp@lazaruscharlotte.com, b.honerkamp@lazaruscharlotte.com</t>
         </is>
       </c>
-      <c r="O143" s="2" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
         <is>
           <t>Team page and rebrand to Lazarus Design Team https://lazarusdesignteam.com/about/</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr">
+      <c r="S143" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11818,14 +11966,15 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" s="2" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr">
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
         <is>
           <t>About page, branding and web design for startups and ecommerce https://webworkshop.ca/about/</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="S144" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -11890,14 +12039,15 @@
           <t>rejected by Icypeas: jason@ohiowebagency.com, jason.apryasz@ohiowebagency.com, jasonapryasz@ohiowebagency.com, japryasz@ohiowebagency.com, j.apryasz@ohiowebagency.com</t>
         </is>
       </c>
-      <c r="O145" s="2" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr">
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
         <is>
           <t>About page, all-inclusive web campaign offer https://www.ohiowebagency.com/about-us/</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
+      <c r="S145" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -11962,14 +12112,15 @@
           <t>rejected by Icypeas: charles@bespokewebdesign.ca</t>
         </is>
       </c>
-      <c r="O146" s="2" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr">
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
         <is>
           <t>About page, founder story and focus on trades https://bespokewebdesign.ca/about/</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr">
+      <c r="S146" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12034,14 +12185,15 @@
           <t>rejected by Icypeas: danielle@fullcircleweb.ca, danielle.hobbs@fullcircleweb.ca, daniellehobbs@fullcircleweb.ca, dhobbs@fullcircleweb.ca, d.hobbs@fullcircleweb.ca</t>
         </is>
       </c>
-      <c r="O147" s="2" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr">
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
         <is>
           <t>Blog, steps to get a Google Grant https://fullcircleweb.ca/9-steps-to-get-a-google-grant/</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="S147" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12106,14 +12258,15 @@
           <t>rejected by Icypeas: adam@emergerichmond.com</t>
         </is>
       </c>
-      <c r="O148" s="2" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr">
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
         <is>
           <t>Case study, Sanford Insurance https://emergerichmond.com/project/in-one-year-775-new-users-found-richmonds-own-sanford-insurance/</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="S148" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12178,14 +12331,15 @@
           <t>rejected by Icypeas: loretta@lynkwebsitedesign.com, loretta.decosse@lynkwebsitedesign.com, lorettadecosse@lynkwebsitedesign.com, ldecosse@lynkwebsitedesign.com, l.decosse@lynkwebsitedesign.com</t>
         </is>
       </c>
-      <c r="O149" s="2" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr">
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
         <is>
           <t>Vancouver Island page, founder still manages projects https://lynkwebsitedesign.com/web-design-vancouver-island</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="S149" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12250,14 +12404,15 @@
           <t>rejected by Icypeas: chris@flamingoagency.com, chris.granat@flamingoagency.com, chrisgranat@flamingoagency.com, cgranat@flamingoagency.com, c.granat@flamingoagency.com</t>
         </is>
       </c>
-      <c r="O150" s="2" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr">
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
         <is>
           <t>Blog, contact page design best practices https://www.flamingoagency.com/blog/contact-page-design/</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="S150" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12322,14 +12477,15 @@
           <t>rejected by Icypeas: ed@kellywebsitedesign.com, ed.kelly@kellywebsitedesign.com, edkelly@kellywebsitedesign.com, ekelly@kellywebsitedesign.com, e.kelly@kellywebsitedesign.com</t>
         </is>
       </c>
-      <c r="O151" s="2" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
         <is>
           <t>About page, small hands-on agency led by Ed Kelly and Kaitlin Farris https://www.kellywebsitedesign.com/about-us/</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
+      <c r="S151" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12394,14 +12550,15 @@
           <t>rejected by Icypeas: anthony@biondocreative.com, anthony.jr@biondocreative.com, anthonyjr@biondocreative.com, ajr@biondocreative.com, a.jr@biondocreative.com</t>
         </is>
       </c>
-      <c r="O152" s="2" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
         <is>
           <t>Press release, Philly Favorites web design company https://www.biondocreative.com/press-releases/2025/philly-favorites-names-biondo-creative-favorite-web-design-company/</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr">
+      <c r="S152" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12466,14 +12623,15 @@
           <t>rejected by Icypeas: william@hiilite.com, william.walczak@hiilite.com, williamwalczak@hiilite.com, wwalczak@hiilite.com, w.walczak@hiilite.com</t>
         </is>
       </c>
-      <c r="O153" s="2" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
         <is>
           <t>Business consulting offer https://hiilite.com/services/business-consulting/</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr">
+      <c r="S153" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12538,14 +12696,15 @@
           <t>rejected by Icypeas: ryan@zealmedia.ca, ryan.boutin@zealmedia.ca, ryanboutin@zealmedia.ca, rboutin@zealmedia.ca, r.boutin@zealmedia.ca</t>
         </is>
       </c>
-      <c r="O154" s="2" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
         <is>
           <t>Blog, not the best first impression https://zealmedia.ca/blog/not-the-best-first-impression/</t>
         </is>
       </c>
-      <c r="R154" t="inlineStr">
+      <c r="S154" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12610,14 +12769,15 @@
           <t>rejected by Icypeas: marie@vegaswebsitedesigns.com</t>
         </is>
       </c>
-      <c r="O155" s="2" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr">
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
         <is>
           <t>About page, founded by Marie and Ryan https://www.vegaswebsitedesigns.com/about/</t>
         </is>
       </c>
-      <c r="R155" t="inlineStr">
+      <c r="S155" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12682,14 +12842,15 @@
           <t>rejected by Icypeas: tj@sacramentowebdesigngroup.com, tj.bernardo@sacramentowebdesigngroup.com, tjbernardo@sacramentowebdesigngroup.com, tbernardo@sacramentowebdesigngroup.com, t.bernardo@sacramentowebdesigngroup.com</t>
         </is>
       </c>
-      <c r="O156" s="2" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
         <is>
           <t>About page, founder's reason for starting https://sacramentowebdesigngroup.com/about/</t>
         </is>
       </c>
-      <c r="R156" t="inlineStr">
+      <c r="S156" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12754,14 +12915,15 @@
           <t>rejected by Icypeas: david@web-design-sacramento.com, david.kovalevich@web-design-sacramento.com, davidkovalevich@web-design-sacramento.com, dkovalevich@web-design-sacramento.com, d.kovalevich@web-design-sacramento.com</t>
         </is>
       </c>
-      <c r="O157" s="2" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr">
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
         <is>
           <t>Press release, May 2025 https://www.financialcontent.com/article/marketersmedia-2025-5-19-web-design-sacramento-by-kova-team-offers-tailored-digital-solutions-for-sacramento-businesses</t>
         </is>
       </c>
-      <c r="R157" t="inlineStr">
+      <c r="S157" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12826,14 +12988,15 @@
           <t>rejected by Icypeas: chuck@team218.com, chuck.hersey@team218.com, chuckhersey@team218.com, chersey@team218.com, c.hersey@team218.com</t>
         </is>
       </c>
-      <c r="O158" s="2" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr">
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr">
         <is>
           <t>Service area page, no deposits and 12 months care https://team218.com/service-areas/des-moines/</t>
         </is>
       </c>
-      <c r="R158" t="inlineStr">
+      <c r="S158" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12898,14 +13061,15 @@
           <t>rejected by Icypeas: luis@denvercountywebdesign.com, luis.castaneda@denvercountywebdesign.com, luiscastaneda@denvercountywebdesign.com, lcastaneda@denvercountywebdesign.com, l.castaneda@denvercountywebdesign.com</t>
         </is>
       </c>
-      <c r="O159" s="2" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr">
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
         <is>
           <t>Free Website Mock Up offer on contact page https://www.denvercountywebdesign.com/contact-us/</t>
         </is>
       </c>
-      <c r="R159" t="inlineStr">
+      <c r="S159" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -12970,14 +13134,15 @@
           <t>rejected by Icypeas: richard@northtexas-webdesign.com, richard.taveira@northtexas-webdesign.com, richardtaveira@northtexas-webdesign.com, rtaveira@northtexas-webdesign.com, r.taveira@northtexas-webdesign.com</t>
         </is>
       </c>
-      <c r="O160" s="2" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr">
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
         <is>
           <t>About page, expansion into Canada as True North Web Design https://northtexas-webdesign.com/about-north-texas-web-design/ . a general address is the address the agency publishes on its own homepage.</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr">
+      <c r="S160" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13042,14 +13207,15 @@
           <t>rejected by Icypeas: danny@starfirewebdesign.com, danny.ericson@starfirewebdesign.com, dannyericson@starfirewebdesign.com, dericson@starfirewebdesign.com, d.ericson@starfirewebdesign.com</t>
         </is>
       </c>
-      <c r="O161" s="2" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr">
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
         <is>
           <t>About page, 'Built by a business owner, not just a developer' https://starfirewebdesign.com/about/</t>
         </is>
       </c>
-      <c r="R161" t="inlineStr">
+      <c r="S161" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13114,14 +13280,15 @@
           <t>rejected by Icypeas: roger@webpro360.com, roger.stanton@webpro360.com, rogerstanton@webpro360.com, rstanton@webpro360.com, r.stanton@webpro360.com</t>
         </is>
       </c>
-      <c r="O162" s="2" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
         <is>
           <t>Team page, Roger Stanton and Tank, est. 2002 https://www.webpro360.com/team/</t>
         </is>
       </c>
-      <c r="R162" t="inlineStr">
+      <c r="S162" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13186,14 +13353,15 @@
           <t>rejected by Icypeas: gurdeep@mangomadness.ca, gurdeep.lall@mangomadness.ca, gurdeeplall@mangomadness.ca, glall@mangomadness.ca, g.lall@mangomadness.ca</t>
         </is>
       </c>
-      <c r="O163" s="2" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr">
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr">
         <is>
           <t>Homepage, web design for lead generation and Greater Saskatoon Chamber endorsement https://mangomadness.ca/</t>
         </is>
       </c>
-      <c r="R163" t="inlineStr">
+      <c r="S163" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13258,14 +13426,15 @@
           <t>rejected by Icypeas: chad@cybernauticdesign.com, chad.parker@cybernauticdesign.com, chadparker@cybernauticdesign.com, cparker@cybernauticdesign.com, c.parker@cybernauticdesign.com</t>
         </is>
       </c>
-      <c r="O164" s="2" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr">
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr">
         <is>
           <t>Meet The Team page https://www.cybernauticdesign.com/about/our-team . a general address is published on the agency's own privacy page. Guesses use cybernauticdesign.com and may need the cybernautic.com domain instead.</t>
         </is>
       </c>
-      <c r="R164" t="inlineStr">
+      <c r="S164" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13330,14 +13499,15 @@
           <t>rejected by Icypeas: hunter@linkcx.com, hunter.carlisle@linkcx.com, huntercarlisle@linkcx.com, hcarlisle@linkcx.com, h.carlisle@linkcx.com</t>
         </is>
       </c>
-      <c r="O165" s="2" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr">
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
         <is>
           <t>About page, History &amp; achievements timeline https://linkcx.com/about-us/</t>
         </is>
       </c>
-      <c r="R165" t="inlineStr">
+      <c r="S165" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13402,14 +13572,15 @@
           <t>rejected by Icypeas: chris@design225.com, chris.hill@design225.com, chrishill@design225.com, chill@design225.com, c.hill@design225.com</t>
         </is>
       </c>
-      <c r="O166" s="2" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr">
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
         <is>
           <t>About page, 'All design is redesign' and founder Chris Hill https://design225.com/about-us/</t>
         </is>
       </c>
-      <c r="R166" t="inlineStr">
+      <c r="S166" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13474,14 +13645,15 @@
           <t>rejected by Icypeas: michael@williamsmedia.co, michael.williams@williamsmedia.co, michaelwilliams@williamsmedia.co, mwilliams@williamsmedia.co, m.williams@williamsmedia.co</t>
         </is>
       </c>
-      <c r="O167" s="2" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr">
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr">
         <is>
           <t>Team Handbook page https://williamsmedia.co/team-handbook ; about page https://williamsmedia.co/about</t>
         </is>
       </c>
-      <c r="R167" t="inlineStr">
+      <c r="S167" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13546,14 +13718,15 @@
           <t>rejected by Icypeas: james@riwebdesign.com, james.kennedy@riwebdesign.com, jameskennedy@riwebdesign.com, jkennedy@riwebdesign.com, j.kennedy@riwebdesign.com</t>
         </is>
       </c>
-      <c r="O168" s="2" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr">
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
         <is>
           <t>Homepage, small jobs into long term accounts https://riwebdesign.com/</t>
         </is>
       </c>
-      <c r="R168" t="inlineStr">
+      <c r="S168" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13618,14 +13791,15 @@
           <t>rejected by Icypeas: mark@scriptablesolutions.com</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr">
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
         <is>
           <t>Blog post on the team's fall favorites https://www.scriptablesolutions.com/articles/tricks-treats-team-spirit-peek-scriptables-fall-favorites . Only the first name Mark is given.</t>
         </is>
       </c>
-      <c r="R169" t="inlineStr">
+      <c r="S169" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13690,14 +13864,15 @@
           <t>rejected by Icypeas: jeremie@ottawawebgenius.com, jeremie.kweto@ottawawebgenius.com, jeremiekweto@ottawawebgenius.com, jkweto@ottawawebgenius.com, j.kweto@ottawawebgenius.com</t>
         </is>
       </c>
-      <c r="O170" s="2" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr">
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr">
         <is>
           <t>About page, Meet the team https://www.ottawawebgenius.com/about/</t>
         </is>
       </c>
-      <c r="R170" t="inlineStr">
+      <c r="S170" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13762,14 +13937,15 @@
           <t>rejected by Icypeas: stephane@fullview.ca, stephane.trottier@fullview.ca, stephanetrottier@fullview.ca, strottier@fullview.ca, s.trottier@fullview.ca</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr">
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
         <is>
           <t>About page, since 2006, founded by Stephane Trottier https://fullview.ca/about/</t>
         </is>
       </c>
-      <c r="R171" t="inlineStr">
+      <c r="S171" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13834,14 +14010,15 @@
           <t>rejected by Icypeas: ivan@solocube.com, ivan.dancourt@solocube.com, ivandancourt@solocube.com, idancourt@solocube.com, i.dancourt@solocube.com</t>
         </is>
       </c>
-      <c r="O172" s="2" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr">
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
         <is>
           <t>About page reviews with owner responses, one naming founder Ivan Dancourt https://solocube.com/about-us/</t>
         </is>
       </c>
-      <c r="R172" t="inlineStr">
+      <c r="S172" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13906,14 +14083,15 @@
           <t>rejected by Icypeas: stacy@brightgreenpath.com, stacy.layman@brightgreenpath.com, stacylayman@brightgreenpath.com, slayman@brightgreenpath.com, s.layman@brightgreenpath.com</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr">
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr">
         <is>
           <t>Blog post on people-centered websites https://brightgreenpath.com/humanizing-your-website-why-people-centered-websites-outperform-ai-optimized-ones/</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
+      <c r="S173" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -13978,14 +14156,15 @@
           <t>rejected by Icypeas: kevin@knoxweb.com, kevin.shick@knoxweb.com, kevinshick@knoxweb.com, kshick@knoxweb.com, k.shick@knoxweb.com</t>
         </is>
       </c>
-      <c r="O174" s="2" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr">
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr">
         <is>
           <t>About page, founded 1997 https://knoxweb.com/about/</t>
         </is>
       </c>
-      <c r="R174" t="inlineStr">
+      <c r="S174" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14050,14 +14229,15 @@
           <t>rejected by Icypeas: joseph@sltcreative.com, joseph.provence@sltcreative.com, josephprovence@sltcreative.com, jprovence@sltcreative.com, j.provence@sltcreative.com</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr">
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr">
         <is>
           <t>About page, founders Joseph &amp; Kaaren Provence https://www.sltcreative.com/about</t>
         </is>
       </c>
-      <c r="R175" t="inlineStr">
+      <c r="S175" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14122,14 +14302,15 @@
           <t>rejected by Icypeas: clayton@webtekcc.com, clayton.kurtz@webtekcc.com, claytonkurtz@webtekcc.com, ckurtz@webtekcc.com, c.kurtz@webtekcc.com</t>
         </is>
       </c>
-      <c r="O176" s="2" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr">
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr">
         <is>
           <t>Our Story page, founder Kornel Kurtz with son and current team leader Clayton Kurtz, started in a converted cistern https://www.webtekcc.com/our-story</t>
         </is>
       </c>
-      <c r="R176" t="inlineStr">
+      <c r="S176" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14194,14 +14375,15 @@
           <t>rejected by Icypeas: sandra@zoomedia.ca, sandra.dugas@zoomedia.ca, sandradugas@zoomedia.ca, sdugas@zoomedia.ca, s.dugas@zoomedia.ca</t>
         </is>
       </c>
-      <c r="O177" s="2" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr">
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr">
         <is>
           <t>Team page, founded by Sandra and Chris Dugas, no revolving door of junior staff https://www.zoomedia.ca/our-team/</t>
         </is>
       </c>
-      <c r="R177" t="inlineStr">
+      <c r="S177" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14266,14 +14448,15 @@
           <t>rejected by Icypeas: andrew@newconceptdesign.com, andrew.wilczynski@newconceptdesign.com, andrewwilczynski@newconceptdesign.com, awilczynski@newconceptdesign.com, a.wilczynski@newconceptdesign.com</t>
         </is>
       </c>
-      <c r="O178" s="2" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr">
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
         <is>
           <t>Site footer, available 7 days a week via email, Andrew Wilczynski Owner https://www.newconceptdesign.com/about-new-concept-design/testimonials</t>
         </is>
       </c>
-      <c r="R178" t="inlineStr">
+      <c r="S178" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14338,14 +14521,15 @@
           <t>rejected by Icypeas: julio@jceseo.com, julio.escamilla@jceseo.com, julioescamilla@jceseo.com, jescamilla@jceseo.com, j.escamilla@jceseo.com</t>
         </is>
       </c>
-      <c r="O179" s="2" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr">
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr">
         <is>
           <t>San Antonio web design page, bilingual design https://www.jceseo.com/san-antonio-web-design/</t>
         </is>
       </c>
-      <c r="R179" t="inlineStr">
+      <c r="S179" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14410,14 +14594,15 @@
           <t>rejected by Icypeas: levi@hogtheweb.com, levi.meulen@hogtheweb.com, levimeulen@hogtheweb.com, lmeulen@hogtheweb.com, l.meulen@hogtheweb.com</t>
         </is>
       </c>
-      <c r="O180" s="2" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr">
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
         <is>
           <t>Ann Arbor page title 'Care and Craft Over Flare and Flash' https://hogtheweb.com/region/ann-arbor-web-design/</t>
         </is>
       </c>
-      <c r="R180" t="inlineStr">
+      <c r="S180" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14482,14 +14667,15 @@
           <t>rejected by Icypeas: alexander@vantagepoint.dev, alexander.nekrassov@vantagepoint.dev, alexandernekrassov@vantagepoint.dev, anekrassov@vantagepoint.dev, a.nekrassov@vantagepoint.dev</t>
         </is>
       </c>
-      <c r="O181" s="2" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr">
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr">
         <is>
           <t>About page, 4 team members and FAQ on ownership and handoff https://vantagepoint.dev/about</t>
         </is>
       </c>
-      <c r="R181" t="inlineStr">
+      <c r="S181" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14554,14 +14740,15 @@
           <t>rejected by Icypeas: beverly@ldrdesignagency.com</t>
         </is>
       </c>
-      <c r="O182" s="2" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr">
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr">
         <is>
           <t>Our Team pages for Cincinnati and Dayton offices https://ldrdesignagency.com/design-team/ . Only the first name Beverly is published.</t>
         </is>
       </c>
-      <c r="R182" t="inlineStr">
+      <c r="S182" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14626,14 +14813,15 @@
           <t>rejected by Icypeas: joella@brandingaloha.com, joella.hopkins@brandingaloha.com, joellahopkins@brandingaloha.com, jhopkins@brandingaloha.com, j.hopkins@brandingaloha.com</t>
         </is>
       </c>
-      <c r="O183" s="2" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr">
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr">
         <is>
           <t>About page, Meet our President Joella Hopkins https://www.brandingaloha.com/about/ . Branding Aloha is part of the Branding Teams group led by CEO Ben Behrooz.</t>
         </is>
       </c>
-      <c r="R183" t="inlineStr">
+      <c r="S183" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14698,14 +14886,15 @@
           <t>rejected by Icypeas: shawn@grafitz.com, shawn.fitzpatrick@grafitz.com, shawnfitzpatrick@grafitz.com, sfitzpatrick@grafitz.com, s.fitzpatrick@grafitz.com</t>
         </is>
       </c>
-      <c r="O184" s="2" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr">
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr">
         <is>
           <t>Meet Our Team, Shawn Fitzpatrick and Ryan Bentley both creative directors and web designers https://grafitz.com/index.php/about-us/the-company</t>
         </is>
       </c>
-      <c r="R184" t="inlineStr">
+      <c r="S184" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14770,14 +14959,15 @@
           <t>rejected by Icypeas: joshua@hellodigital.marketing, joshua.hay@hellodigital.marketing, joshuahay@hellodigital.marketing, jhay@hellodigital.marketing, j.hay@hellodigital.marketing</t>
         </is>
       </c>
-      <c r="O185" s="2" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr">
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr">
         <is>
           <t>Learn section articles by founder Joshua Hay on WordPress security https://www.hellodigital.marketing/ ; team page https://www.hellodigital.marketing/about-hello-digital-marketing-winnipeg/</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr">
+      <c r="S185" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14826,14 +15016,15 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
-      <c r="O186" s="2" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr">
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr">
         <is>
           <t>Industries We Serve pages https://desmoinescreative.com/industries-we-serve/ . A web search summary named Ashley Miller as owner but no page confirming it could be opened, so no name recorded.</t>
         </is>
       </c>
-      <c r="R186" t="inlineStr">
+      <c r="S186" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -14898,14 +15089,15 @@
           <t>rejected by Icypeas: rafael@royalinkdesign.com, rafael.rivas@royalinkdesign.com, rafaelrivas@royalinkdesign.com, rrivas@royalinkdesign.com, r.rivas@royalinkdesign.com</t>
         </is>
       </c>
-      <c r="O187" s="2" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr">
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr">
         <is>
           <t>Meet Your Team page, 'NO CONTRACTS' https://royalinkdesign.com/meet-your-team/</t>
         </is>
       </c>
-      <c r="R187" t="inlineStr">
+      <c r="S187" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -14954,14 +15146,15 @@
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" s="2" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr">
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr">
         <is>
           <t>About page, flat pricing and no contracts https://slynerds.com/about . The founder is not named on the site. A LinkedIn search result lists Casey Margolis at Sly Nerds (https://www.linkedin.com/in/casey-margolis-305a90172/) but the profile could not be opened to confirm the role.</t>
         </is>
       </c>
-      <c r="R188" t="inlineStr">
+      <c r="S188" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -15010,14 +15203,15 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" s="2" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr">
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr">
         <is>
           <t>Homepage services and footer 'Copyright 2002 - 2025' https://www.webstudioboston.com/ . No owner named on the site; a client testimonial thanks 'Paul' but his role isn't stated.</t>
         </is>
       </c>
-      <c r="R189" t="inlineStr">
+      <c r="S189" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -15066,14 +15260,15 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" s="2" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr">
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr">
         <is>
           <t>Homepage, 'No Outsourcing' and 'small, friendly team' https://websites.ca/ . A search result lists John Hart as co-founder (https://websites.ca/author/johnhart/) but that page redirects to the homepage, so the name isn't recorded. Model is package based WordPress sites.</t>
         </is>
       </c>
-      <c r="R190" t="inlineStr">
+      <c r="S190" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -15138,14 +15333,15 @@
           <t>rejected by Icypeas: nathan@charlotteweb.design, nathan.robinson@charlotteweb.design, nathanrobinson@charlotteweb.design, nrobinson@charlotteweb.design, n.robinson@charlotteweb.design</t>
         </is>
       </c>
-      <c r="O191" s="2" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr">
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr">
         <is>
           <t>Homepage, Meet The Founder section https://charlotteweb.design/</t>
         </is>
       </c>
-      <c r="R191" t="inlineStr">
+      <c r="S191" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15194,14 +15390,15 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
-      <c r="O192" s="2" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr">
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr">
         <is>
           <t>Homepage title and copy https://www.multimediaxp.com/ . The site shows Eduardo Ponce de Leon as a blog author and mario@, brandon@ addresses, but no one is named as owner.</t>
         </is>
       </c>
-      <c r="R192" t="inlineStr">
+      <c r="S192" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -15266,14 +15463,15 @@
           <t>rejected by Icypeas: brian@agency317.com, brian.yerkes@agency317.com, brianyerkes@agency317.com, byerkes@agency317.com, b.yerkes@agency317.com</t>
         </is>
       </c>
-      <c r="O193" s="2" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr">
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr">
         <is>
           <t>About page, Our Team with Brian Yerkes Founder / Designer https://agency317.com/about/</t>
         </is>
       </c>
-      <c r="R193" t="inlineStr">
+      <c r="S193" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15338,14 +15536,15 @@
           <t>rejected by Icypeas: phong@proweb365.com, phong.nguyen@proweb365.com, phongnguyen@proweb365.com, pnguyen@proweb365.com, p.nguyen@proweb365.com</t>
         </is>
       </c>
-      <c r="O194" s="2" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr">
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr">
         <is>
           <t>Homepage, 'founded in 2009 by Phong Nguyen' and client reviews naming Phong https://proweb365.com/</t>
         </is>
       </c>
-      <c r="R194" t="inlineStr">
+      <c r="S194" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15394,14 +15593,15 @@
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
-      <c r="O195" s="2" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr">
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr">
         <is>
           <t>About page and homepage work, Heartland Utility Services https://animusdigital.co/about/ . Founder not named on the site.</t>
         </is>
       </c>
-      <c r="R195" t="inlineStr">
+      <c r="S195" t="inlineStr">
         <is>
           <t>missing: owner name, owner email, opening line</t>
         </is>
@@ -15466,14 +15666,15 @@
           <t>rejected by Icypeas: terry@bestwebdesigntucson.com, terry.samuels@bestwebdesigntucson.com, terrysamuels@bestwebdesigntucson.com, tsamuels@bestwebdesigntucson.com, t.samuels@bestwebdesigntucson.com</t>
         </is>
       </c>
-      <c r="O196" s="2" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr">
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr">
         <is>
           <t>Homepage, 'Terry Samuels Founder, answering the phone himself' https://bestwebdesigntucson.com/</t>
         </is>
       </c>
-      <c r="R196" t="inlineStr">
+      <c r="S196" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15538,14 +15739,15 @@
           <t>rejected by Icypeas: joel@360psg.com, joel.colombo@360psg.com, joelcolombo@360psg.com, jcolombo@360psg.com, j.colombo@360psg.com</t>
         </is>
       </c>
-      <c r="O197" s="2" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr">
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr">
         <is>
           <t>Homepage team section, Joel Colombo President https://www.360psg.com/</t>
         </is>
       </c>
-      <c r="R197" t="inlineStr">
+      <c r="S197" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15610,14 +15812,15 @@
           <t>rejected by Icypeas: tom@ezmarketing.com, tom.malesic@ezmarketing.com, tommalesic@ezmarketing.com, tmalesic@ezmarketing.com, t.malesic@ezmarketing.com</t>
         </is>
       </c>
-      <c r="O198" s="2" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr">
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
         <is>
           <t>About page, 'just a small in-house team' https://www.ezmarketing.com/about/</t>
         </is>
       </c>
-      <c r="R198" t="inlineStr">
+      <c r="S198" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15682,14 +15885,15 @@
           <t>rejected by Icypeas: subodh@marvelwebsites.com</t>
         </is>
       </c>
-      <c r="O199" s="2" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr">
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" s="2" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr">
         <is>
           <t>Team page and homepage reviews naming Subodh https://marvelwebsites.com/marvel-websites-team/ . Only the first name is published.</t>
         </is>
       </c>
-      <c r="R199" t="inlineStr">
+      <c r="S199" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15754,14 +15958,15 @@
           <t>rejected by Icypeas: rick@websitedesignkingston.com</t>
         </is>
       </c>
-      <c r="O200" s="2" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr">
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" s="2" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr">
         <is>
           <t>About page team bios https://websitedesignkingston.com/about-us/ . Only the first name Rick is published.</t>
         </is>
       </c>
-      <c r="R200" t="inlineStr">
+      <c r="S200" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15826,14 +16031,15 @@
           <t>rejected by Icypeas: angela@oklahomawebdesign.com, angela.drabek@oklahomawebdesign.com, angeladrabek@oklahomawebdesign.com, adrabek@oklahomawebdesign.com, a.drabek@oklahomawebdesign.com</t>
         </is>
       </c>
-      <c r="O201" s="2" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr">
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" s="2" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
         <is>
           <t>About page, Oklahoma owned and operated since 1997 by founder Angela Drabek https://oklahomawebdesign.com/about/</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr">
+      <c r="S201" t="inlineStr">
         <is>
           <t>missing: owner email, opening line</t>
         </is>
@@ -15874,14 +16080,15 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr">
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" s="2" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr">
         <is>
           <t>https://www.gasmandesign.com/about/</t>
         </is>
       </c>
-      <c r="R202" t="inlineStr">
+      <c r="S202" t="inlineStr">
         <is>
           <t>skip: solo freelancer (founder describes himself as a freelance website designer)</t>
         </is>
@@ -15922,14 +16129,15 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" s="2" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr">
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" s="2" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr">
         <is>
           <t>https://www.brightsidekc.com/about</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr">
+      <c r="S203" t="inlineStr">
         <is>
           <t>skip: two-person studio (Katie and Jess), well under 5 people</t>
         </is>
@@ -15970,14 +16178,15 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr">
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr">
         <is>
           <t>https://www.objective.dev/about/</t>
         </is>
       </c>
-      <c r="R204" t="inlineStr">
+      <c r="S204" t="inlineStr">
         <is>
           <t>skip: primarily a software and app development shop</t>
         </is>
@@ -16018,14 +16227,15 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
-      <c r="O205" s="2" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr">
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" s="2" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr">
         <is>
           <t>https://www.roketco.com/</t>
         </is>
       </c>
-      <c r="R205" t="inlineStr">
+      <c r="S205" t="inlineStr">
         <is>
           <t>skip: primarily an app design and development agency</t>
         </is>
@@ -16066,14 +16276,15 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
-      <c r="O206" s="2" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr">
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
         <is>
           <t>https://www.goldenlaunchcreative.com/shop-templates/charlene-squarespace-template</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr">
+      <c r="S206" t="inlineStr">
         <is>
           <t>skip: sells Squarespace templates alongside services, and appears founder-only</t>
         </is>
@@ -16114,14 +16325,15 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
-      <c r="O207" s="2" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr">
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" s="2" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr">
         <is>
           <t>https://louisvillewebnerds.com/about/</t>
         </is>
       </c>
-      <c r="R207" t="inlineStr">
+      <c r="S207" t="inlineStr">
         <is>
           <t>skip: appears to be a solo operator (Cody Wheeler)</t>
         </is>
@@ -16162,14 +16374,15 @@
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
-      <c r="O208" s="2" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr">
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" s="2" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr">
         <is>
           <t>https://kdesign.co/</t>
         </is>
       </c>
-      <c r="R208" t="inlineStr">
+      <c r="S208" t="inlineStr">
         <is>
           <t>skip: solo designer</t>
         </is>
@@ -16210,14 +16423,15 @@
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
-      <c r="O209" s="2" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr">
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
         <is>
           <t>https://www.wisegrowthmarketing.com/service/free-website-diy/</t>
         </is>
       </c>
-      <c r="R209" t="inlineStr">
+      <c r="S209" t="inlineStr">
         <is>
           <t>skip: sells Wix and free DIY template websites</t>
         </is>
@@ -16258,14 +16472,15 @@
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
-      <c r="O210" s="2" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr">
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
         <is>
           <t>https://www.dallaswebagency.us/</t>
         </is>
       </c>
-      <c r="R210" t="inlineStr">
+      <c r="S210" t="inlineStr">
         <is>
           <t>skip: is itself a white-label web agency (competitor, not a prospect)</t>
         </is>
@@ -16306,14 +16521,15 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
-      <c r="O211" s="2" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr">
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
         <is>
           <t>https://m5designstudio.com/services/</t>
         </is>
       </c>
-      <c r="R211" t="inlineStr">
+      <c r="S211" t="inlineStr">
         <is>
           <t>skip: about 3 employees and markets WordPress templates</t>
         </is>
@@ -16354,14 +16570,15 @@
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
-      <c r="O212" s="2" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr">
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
         <is>
           <t>https://www.aquarianwebdesign.com/about-aquarian/working-here and homepage: 'A trusted expert website partner for businesses and agencies'</t>
         </is>
       </c>
-      <c r="R212" t="inlineStr">
+      <c r="S212" t="inlineStr">
         <is>
           <t>skip: markets itself as a go-to web provider to advertising agencies (competitor, rule 19)</t>
         </is>
@@ -16402,14 +16619,15 @@
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
-      <c r="O213" s="2" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr">
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" s="2" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr">
         <is>
           <t>https://saltdstudio.com/about</t>
         </is>
       </c>
-      <c r="R213" t="inlineStr">
+      <c r="S213" t="inlineStr">
         <is>
           <t>skip: two-person studio (Cameron and Emma Rodger), well under 5 people</t>
         </is>
@@ -16450,14 +16668,15 @@
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
-      <c r="O214" s="2" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr">
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" s="2" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr">
         <is>
           <t>https://coloradowebimpressions.com/team</t>
         </is>
       </c>
-      <c r="R214" t="inlineStr">
+      <c r="S214" t="inlineStr">
         <is>
           <t>skip: owner-operated, owner does the work himself (team page lists only the founder and lead practitioner)</t>
         </is>
@@ -16498,14 +16717,15 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
-      <c r="O215" s="2" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr">
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr">
         <is>
           <t>https://guru.digital808.com/web-design-team-in-middlesex-county-boston/</t>
         </is>
       </c>
-      <c r="R215" t="inlineStr">
+      <c r="S215" t="inlineStr">
         <is>
           <t>skip: three-person studio per its team page ('A Developer, a Designer, and an SEO Guru'), under 5 people</t>
         </is>
@@ -16546,14 +16766,15 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
-      <c r="O216" s="2" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr">
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" s="2" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr">
         <is>
           <t>https://www.plaidbuffalocreative.com/</t>
         </is>
       </c>
-      <c r="R216" t="inlineStr">
+      <c r="S216" t="inlineStr">
         <is>
           <t>skip: two-partner studio that never subcontracts (Lindsay Creedon and Fraser Mackenzie), under 5 people</t>
         </is>
@@ -16594,14 +16815,15 @@
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" s="2" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr">
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr">
         <is>
           <t>https://www.winnipegwebguy.ca/about-us/</t>
         </is>
       </c>
-      <c r="R217" t="inlineStr">
+      <c r="S217" t="inlineStr">
         <is>
           <t>skip: solo operator (Todd, the Winnipeg Web Guy)</t>
         </is>
@@ -16642,14 +16864,15 @@
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
-      <c r="O218" s="2" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr">
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" s="2" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr">
         <is>
           <t>https://citylifestyle.com/articles/jlb-getting-down-to-business</t>
         </is>
       </c>
-      <c r="R218" t="inlineStr">
+      <c r="S218" t="inlineStr">
         <is>
           <t>skip: too large, describes itself as the largest web design and digital marketing agency in the Nashville area with 650+ brands</t>
         </is>
@@ -16690,14 +16913,15 @@
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
-      <c r="O219" s="2" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr">
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" s="2" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr">
         <is>
           <t>https://www.directallied.com/</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr">
+      <c r="S219" t="inlineStr">
         <is>
           <t>skip: sells private label web design to agencies (competitor, rule 19)</t>
         </is>
@@ -16738,14 +16962,15 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
-      <c r="O220" s="2" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr">
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr">
         <is>
           <t>https://limeglowdesign.com/about-us/</t>
         </is>
       </c>
-      <c r="R220" t="inlineStr">
+      <c r="S220" t="inlineStr">
         <is>
           <t>skip: three-person family studio (Shane, Andrea and Charlie Fell), under 5 people</t>
         </is>
@@ -16786,14 +17011,15 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
-      <c r="O221" s="2" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr">
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" s="2" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr">
         <is>
           <t>https://ravenseyedesign.com/about/</t>
         </is>
       </c>
-      <c r="R221" t="inlineStr">
+      <c r="S221" t="inlineStr">
         <is>
           <t>skip: solo designer (about page written in first person)</t>
         </is>
@@ -16834,14 +17060,15 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" s="2" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr">
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" s="2" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr">
         <is>
           <t>https://outcareyourcompetition.com/about/</t>
         </is>
       </c>
-      <c r="R222" t="inlineStr">
+      <c r="S222" t="inlineStr">
         <is>
           <t>skip: primarily a local SEO company run by one person (Jordan J. Caron)</t>
         </is>
@@ -16882,14 +17109,15 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
-      <c r="O223" s="2" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr">
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr">
         <is>
           <t>https://www.columbuswebseo.com/about/</t>
         </is>
       </c>
-      <c r="R223" t="inlineStr">
+      <c r="S223" t="inlineStr">
         <is>
           <t>skip: solo operator, owner Matt McWilliam designs and builds every site himself</t>
         </is>
@@ -16930,14 +17158,15 @@
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
-      <c r="O224" s="2" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr">
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr">
         <is>
           <t>https://www.southtowndesigns.com/about-us/</t>
         </is>
       </c>
-      <c r="R224" t="inlineStr">
+      <c r="S224" t="inlineStr">
         <is>
           <t>skip: owner-led, clients work directly with Michael who designs and builds each site (effectively solo)</t>
         </is>
@@ -16978,14 +17207,15 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" s="2" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr">
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" s="2" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr">
         <is>
           <t>https://liftedlogic.com/meet-the-team/</t>
         </is>
       </c>
-      <c r="R225" t="inlineStr">
+      <c r="S225" t="inlineStr">
         <is>
           <t>skip: too large, about 100 employees per its team page</t>
         </is>
@@ -17026,14 +17256,15 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
-      <c r="O226" s="2" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr">
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr">
         <is>
           <t>https://capitaldistrictdigital.com/about/</t>
         </is>
       </c>
-      <c r="R226" t="inlineStr">
+      <c r="S226" t="inlineStr">
         <is>
           <t>skip: two-person husband and wife team that does the work themselves (Anthony and Kaila Troia)</t>
         </is>
@@ -17074,14 +17305,15 @@
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
-      <c r="O227" s="2" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr">
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" s="2" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr">
         <is>
           <t>https://lubbockdesign.net/about</t>
         </is>
       </c>
-      <c r="R227" t="inlineStr">
+      <c r="S227" t="inlineStr">
         <is>
           <t>skip: solo operator ('One person. Every service.')</t>
         </is>
@@ -17122,14 +17354,15 @@
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
-      <c r="O228" s="2" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr">
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" s="2" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr">
         <is>
           <t>https://www.clemsonwebdesign.com/about-clemson-web-design/</t>
         </is>
       </c>
-      <c r="R228" t="inlineStr">
+      <c r="S228" t="inlineStr">
         <is>
           <t>skip: solo operator (owner Daniel Seymour works one on one with every client)</t>
         </is>
@@ -17170,14 +17403,15 @@
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
-      <c r="O229" s="2" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr">
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" s="2" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr">
         <is>
           <t>Services menu, 'WordPress white label' and 'Sell my web design company' https://freshysites.com/</t>
         </is>
       </c>
-      <c r="R229" t="inlineStr">
+      <c r="S229" t="inlineStr">
         <is>
           <t>skip: offers WordPress white label services to agencies and buys web design companies (competitor, rule 19)</t>
         </is>
@@ -17218,14 +17452,15 @@
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
-      <c r="O230" s="2" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr">
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" s="2" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr">
         <is>
           <t>https://braggmedia.com/about-bragg-media/</t>
         </is>
       </c>
-      <c r="R230" t="inlineStr">
+      <c r="S230" t="inlineStr">
         <is>
           <t>skip: three people on the team page, under 5</t>
         </is>
